--- a/tests/testdata/excels/invalid/RefMissing.xlsx
+++ b/tests/testdata/excels/invalid/RefMissing.xlsx
@@ -2,7 +2,7 @@
 <file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
-    <t>*id</t>
+    <t>id#</t>
   </si>
   <si>
     <t>itemRef</t>
